--- a/Result/profitability/6294.xlsx
+++ b/Result/profitability/6294.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23625</v>
+        <v>0.5912499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>27.65375</v>
+        <v>30.40875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26625</v>
+        <v>0.49375</v>
       </c>
       <c r="N3" t="n">
-        <v>28.4</v>
+        <v>30.2475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.215</v>
+        <v>0.48</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.321249999999999</v>
+        <v>1.083749999999998</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1875</v>
+        <v>0.1925</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.605</v>
+        <v>-4.726250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09375000000000004</v>
+        <v>0.125</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.5625</v>
+        <v>-8.387500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14875</v>
+        <v>0.11625</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.21125</v>
+        <v>-11.895</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1625</v>
+        <v>0.12125</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.68875</v>
+        <v>-15.79875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.06</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1612500000000001</v>
+        <v>-0.16125</v>
       </c>
       <c r="N9" t="n">
         <v>-20.3025</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6294</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>259</v>
+      </c>
+      <c r="D75" t="n">
+        <v>137</v>
+      </c>
+      <c r="E75" t="n">
+        <v>122</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>69</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>69</v>
+      </c>
+      <c r="K75" t="n">
+        <v>57</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.7825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-32.42857142857143</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4735358596930785</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.0185185185185186</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.970000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02019991670137455</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
